--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>105111657</v>
       </c>
       <c r="B2" t="n">
-        <v>97512</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723329.6358029982</v>
+        <v>723330</v>
       </c>
       <c r="R2" t="n">
-        <v>6393644.248180774</v>
+        <v>6393644</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>1992-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1992-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>105111646</v>
       </c>
       <c r="B3" t="n">
-        <v>97518</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723339.2621231457</v>
+        <v>723339</v>
       </c>
       <c r="R3" t="n">
-        <v>6393664.632726629</v>
+        <v>6393665</v>
       </c>
       <c r="S3" t="n">
         <v>71</v>
@@ -883,19 +863,9 @@
           <t>1983-10-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1983-10-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -939,12 +909,7 @@
         <v>105111577</v>
       </c>
       <c r="B4" t="n">
-        <v>97822</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723208.6814435386</v>
+        <v>723209</v>
       </c>
       <c r="R4" t="n">
-        <v>6393692.83642148</v>
+        <v>6393693</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,19 +974,9 @@
           <t>1992-08-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1992-08-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105111657</v>
       </c>
       <c r="B2" t="n">
-        <v>99796</v>
+        <v>99802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>105111646</v>
       </c>
       <c r="B3" t="n">
-        <v>99802</v>
+        <v>99808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>105111577</v>
       </c>
       <c r="B4" t="n">
-        <v>100109</v>
+        <v>100115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105111657</v>
       </c>
       <c r="B2" t="n">
-        <v>99802</v>
+        <v>99805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>105111646</v>
       </c>
       <c r="B3" t="n">
-        <v>99808</v>
+        <v>99811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>105111577</v>
       </c>
       <c r="B4" t="n">
-        <v>100115</v>
+        <v>100119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105111657</v>
       </c>
       <c r="B2" t="n">
-        <v>99805</v>
+        <v>99810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>105111646</v>
       </c>
       <c r="B3" t="n">
-        <v>99811</v>
+        <v>99816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>105111577</v>
       </c>
       <c r="B4" t="n">
-        <v>100119</v>
+        <v>100125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105111657</v>
       </c>
       <c r="B2" t="n">
-        <v>99810</v>
+        <v>99811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>105111646</v>
       </c>
       <c r="B3" t="n">
-        <v>99816</v>
+        <v>99817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>105111577</v>
       </c>
       <c r="B4" t="n">
-        <v>100125</v>
+        <v>100126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105111657</v>
       </c>
       <c r="B2" t="n">
-        <v>99811</v>
+        <v>99838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>105111646</v>
       </c>
       <c r="B3" t="n">
-        <v>99817</v>
+        <v>99844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>105111577</v>
       </c>
       <c r="B4" t="n">
-        <v>100126</v>
+        <v>100153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105111657</v>
       </c>
       <c r="B2" t="n">
-        <v>99838</v>
+        <v>99844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>105111646</v>
       </c>
       <c r="B3" t="n">
-        <v>99844</v>
+        <v>99850</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>105111577</v>
       </c>
       <c r="B4" t="n">
-        <v>100153</v>
+        <v>100159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105111657</v>
       </c>
       <c r="B2" t="n">
-        <v>99844</v>
+        <v>99851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>105111646</v>
       </c>
       <c r="B3" t="n">
-        <v>99850</v>
+        <v>99857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>105111577</v>
       </c>
       <c r="B4" t="n">
-        <v>100159</v>
+        <v>100166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105111657</v>
       </c>
       <c r="B2" t="n">
-        <v>99851</v>
+        <v>99855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>105111646</v>
       </c>
       <c r="B3" t="n">
-        <v>99857</v>
+        <v>99861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>105111577</v>
       </c>
       <c r="B4" t="n">
-        <v>100166</v>
+        <v>100170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105111657</v>
       </c>
       <c r="B2" t="n">
-        <v>99855</v>
+        <v>99862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>105111646</v>
       </c>
       <c r="B3" t="n">
-        <v>99861</v>
+        <v>99868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>105111577</v>
       </c>
       <c r="B4" t="n">
-        <v>100170</v>
+        <v>100177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105111657</v>
       </c>
       <c r="B2" t="n">
-        <v>99865</v>
+        <v>99870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>105111646</v>
       </c>
       <c r="B3" t="n">
-        <v>99871</v>
+        <v>99876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>105111577</v>
       </c>
       <c r="B4" t="n">
-        <v>100180</v>
+        <v>100185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105111657</v>
       </c>
       <c r="B2" t="n">
-        <v>99870</v>
+        <v>99878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>105111646</v>
       </c>
       <c r="B3" t="n">
-        <v>99876</v>
+        <v>99884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>105111577</v>
       </c>
       <c r="B4" t="n">
-        <v>100185</v>
+        <v>100193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32718-2021 artfynd.xlsx
+++ b/artfynd/A 32718-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>105111657</v>
       </c>
       <c r="B2" t="n">
-        <v>99878</v>
+        <v>100347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>105111646</v>
       </c>
       <c r="B3" t="n">
-        <v>99884</v>
+        <v>100353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,32 +906,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105111577</v>
+        <v>105111655</v>
       </c>
       <c r="B4" t="n">
-        <v>100193</v>
+        <v>100353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>783</v>
+        <v>178</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skugglosta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Bromopsis ramosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(Huds.) Holub</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723209</v>
+        <v>723239</v>
       </c>
       <c r="R4" t="n">
-        <v>6393693</v>
+        <v>6393653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,11 +979,6 @@
           <t>1992-08-08</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gothem, Botvalde 1:30 (6); tidigare Boge, Tjälder 1:13 II</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -995,7 +990,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Granskog.</t>
+          <t>Hygge med rörligt grundvatten, f.d. granskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1010,6 +1005,117 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>105111577</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100666</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>783</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogskorn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hordelymus europaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tjelvars grav 600 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>723209</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6393693</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gothem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1992-08-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1992-08-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gothem, Botvalde 1:30 (6); tidigare Boge, Tjälder 1:13 II</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Granskog.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
         </is>
